--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0003T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0003T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.35040749075868</v>
+        <v>7.856941217248287</v>
       </c>
       <c r="D2" t="n">
-        <v>48.46171190467093</v>
+        <v>7.875028184509027</v>
       </c>
       <c r="E2" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F2" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.84961003781395</v>
+        <v>8.263061631144767</v>
       </c>
       <c r="D3" t="n">
-        <v>51.13231223698821</v>
+        <v>8.309000738510585</v>
       </c>
       <c r="E3" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F3" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.83890641445703</v>
+        <v>7.123822292349267</v>
       </c>
       <c r="D4" t="n">
-        <v>43.77808778967974</v>
+        <v>7.113939265822958</v>
       </c>
       <c r="E4" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F4" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.90685839977876</v>
+        <v>7.297364489964049</v>
       </c>
       <c r="D5" t="n">
-        <v>45.22179330414081</v>
+        <v>7.348541411922882</v>
       </c>
       <c r="E5" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F5" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.84908418760233</v>
+        <v>5.987976180485378</v>
       </c>
       <c r="D6" t="n">
-        <v>36.26101396938178</v>
+        <v>5.892414770024539</v>
       </c>
       <c r="E6" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F6" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>52.39804996416829</v>
+        <v>8.514683119177349</v>
       </c>
       <c r="D7" t="n">
-        <v>38.58582533722736</v>
+        <v>6.270196617299447</v>
       </c>
       <c r="E7" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F7" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.59191528689185</v>
+        <v>6.596186234119926</v>
       </c>
       <c r="D8" t="n">
-        <v>33.38002646786546</v>
+        <v>5.424254301028137</v>
       </c>
       <c r="E8" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F8" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.37003941524654</v>
+        <v>5.585131404977564</v>
       </c>
       <c r="D9" t="n">
-        <v>33.31844439900438</v>
+        <v>5.414247214838212</v>
       </c>
       <c r="E9" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F9" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>50.39897820857095</v>
+        <v>8.18983395889278</v>
       </c>
       <c r="D10" t="n">
-        <v>28.00407429385166</v>
+        <v>4.550662072750895</v>
       </c>
       <c r="E10" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F10" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>19.5746890595541</v>
+        <v>3.180886972177541</v>
       </c>
       <c r="D11" t="n">
-        <v>18.84700213521636</v>
+        <v>3.062637846972658</v>
       </c>
       <c r="E11" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F11" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>32.8497677521442</v>
+        <v>5.338087259723433</v>
       </c>
       <c r="D12" t="n">
-        <v>31.62187184666076</v>
+        <v>5.138554175082374</v>
       </c>
       <c r="E12" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F12" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>5.565613978780865</v>
+        <v>0.9044122715518906</v>
       </c>
       <c r="D13" t="n">
-        <v>6.458863096619853</v>
+        <v>1.049565253200726</v>
       </c>
       <c r="E13" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F13" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>7.442374594492727</v>
+        <v>1.209385871605068</v>
       </c>
       <c r="D14" t="n">
-        <v>6.274952401924804</v>
+        <v>1.019679765312781</v>
       </c>
       <c r="E14" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F14" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>29.2192426935389</v>
+        <v>4.748126937700071</v>
       </c>
       <c r="D15" t="n">
-        <v>28.19830004388962</v>
+        <v>4.582223757132063</v>
       </c>
       <c r="E15" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F15" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>46.13033909790114</v>
+        <v>7.496180103408935</v>
       </c>
       <c r="D16" t="n">
-        <v>9.552551792514745</v>
+        <v>1.552289666283646</v>
       </c>
       <c r="E16" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F16" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>29.42519825299814</v>
+        <v>4.781594716112198</v>
       </c>
       <c r="D17" t="n">
-        <v>28.61249095129834</v>
+        <v>4.649529779585981</v>
       </c>
       <c r="E17" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F17" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>25.23089846857332</v>
+        <v>4.100021001143165</v>
       </c>
       <c r="D18" t="n">
-        <v>24.90663237855757</v>
+        <v>4.047327761515605</v>
       </c>
       <c r="E18" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F18" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>44.76457043954801</v>
+        <v>7.274242696426552</v>
       </c>
       <c r="D19" t="n">
-        <v>43.88743676713113</v>
+        <v>7.131708474658809</v>
       </c>
       <c r="E19" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F19" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>22.81707455155762</v>
+        <v>3.707774614628114</v>
       </c>
       <c r="D20" t="n">
-        <v>20.04704655851117</v>
+        <v>3.257645065758066</v>
       </c>
       <c r="E20" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F20" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>46.38374124193091</v>
+        <v>7.537357951813774</v>
       </c>
       <c r="D21" t="n">
-        <v>46.26696586192052</v>
+        <v>7.518381952562084</v>
       </c>
       <c r="E21" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F21" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>47.05086174891906</v>
+        <v>7.645765034199347</v>
       </c>
       <c r="D22" t="n">
-        <v>47.255728460561</v>
+        <v>7.679055874841163</v>
       </c>
       <c r="E22" t="n">
-        <v>13.49416564117899</v>
+        <v>2.192801916691586</v>
       </c>
       <c r="F22" t="n">
-        <v>13.48616055685478</v>
+        <v>2.191501090488902</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
